--- a/rod_hotels_flattened.xlsx
+++ b/rod_hotels_flattened.xlsx
@@ -441,712 +441,712 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__code_h__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__complete_par_le_user_au_moment_de_la_connexion</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__code_h</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__nom_de_l_hotel__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__remonte_automatiquement</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__nom_de_l_hotel</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_1__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_2__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_3__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__code_postal__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__code_postal</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__ville__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__ville</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__longitude__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__export_a_la_demande__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__longitude</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__latitude__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__export_a_la_demande__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__latitude</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__marque__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_fichier_parametres_regles_projections_nb_d_hotels</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__marque</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_fichier_parametres_regles_projections_nb_d_hotels</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_signe_annee__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_signe_annee</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_type__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_type</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__proprietaire__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__proprietaire</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__dom_dof__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__dom_dof</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_hotel__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_hotel</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_lobby__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_lobby</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__pms__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__pms</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__adultes_par_chambre__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__adultes_par_chambre</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__enfants_par_chambre__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__enfants_par_chambre</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__panier_moyen__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__panier_moyen</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_annuel__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_1_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_annuel</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_bas_mois__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_le_calcul_de_la_simulation_de_revenu_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_bas_mois</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_bas_taux__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_le_calcul_de_la_simulation_de_revenu_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_bas_taux</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_mois__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_le_calcul_de_la_simulation_de_revenu_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_mois</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_taux__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_le_calcul_de_la_simulation_de_revenu_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_taux</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__a_proximite_a_100m__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__a_proximite_a_100m</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_restauration__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__31</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_restauration__source_row__31</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_supermarches__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__32</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_supermarches__source_row__32</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_autres_commerces__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__33</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_autres_commerces__source_row__33</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__a_proximite_a_500m__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__a_proximite_a_500m</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_restauration__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__35</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_restauration__source_row__35</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_supermarches__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__36</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_supermarches__source_row__36</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_autres_commerces__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_google__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__37</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__localisation_environnement__data__nb_autres_commerces__source_row__37</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__39</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__source_row__39</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__40</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__source_row__40</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__41</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__source_row__41</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__43</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__source_row__43</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__44</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__source_row__44</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__45</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__source_row__45</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__room_service__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__room_service</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__minibar__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__minibar</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__spa__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__spa</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__si_l_hotel_possede_deja_une_vitrine_refrigeree_standard_et_que_le_corner_recommande_est_easy_ou_liberty_alors_le_nb_de_vitrine_a_acheter_est_a_0</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__assises__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__assises</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs_individuels__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs_individuels</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_solo__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_solo</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs_groupes__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs_groupes</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires_individuels__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires_individuels</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires_groupes__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires_groupes</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__national__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__national</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__international__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__international</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_non_alcoolisees__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_non_alcoolisees</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_secs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_secs</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_secs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_secs</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_sos__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_sos</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__hygiene__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__hygiene</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__ajouter_fonctionnalite_permettant_a_l_hotel_de_conserver_l_agencement_de_son_corner_existant</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__85</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__85</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__86</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__86</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__87</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__87</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__88</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__88</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__89</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__89</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__canaux_de_vente__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__canaux_de_vente</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__frigo_connecte__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__frigo_connecte</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__caisse_code_barres__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__caisse_code_barres</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reappro__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reappro</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__fournisseur__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__fournisseur</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__99</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__99</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__100</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__100</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__101</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__101</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__102</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__102</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__103</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__103</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__canaux_de_vente__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__canaux_de_vente</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__armoire_connectee__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__armoire_connectee</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__caisse_code_barres__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__caisse_code_barres</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reappro__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reappro</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__fournisseur__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__fournisseur</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__x_de_mes_clients_passent_devant_ce_corner__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__ce_qui_est_utilise_ici_lors_de_la_simulation_c_est_la_moyenne_constatee_dans_le_cadre_des_pilotes</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__x_de_mes_clients_passent_devant_ce_corner</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_lineaires_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_4_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_lineaires_estimation</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_carres_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_carres_estimation</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__115</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__source_row__115</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__116</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__source_row__116</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__117</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__source_row__117</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__118</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__source_row__118</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__x_de_mes_clients_passent_devant_cet_emplacement__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__ce_qui_est_utilise_ici_lors_de_la_simulation_c_est_la_moyenne_constatee_dans_le_cadre_des_pilotes</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__x_de_mes_clients_passent_devant_cet_emplacement</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__metres_lineaires_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_4_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__metres_lineaires_estimation</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__metres_carres_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__autre_emplacement_dispo__data__metres_carres_estimation</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__122</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__source_row__122</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__123</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__source_row__123</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__124</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__source_row__124</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__125</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__source_row__125</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__nb_de_chambres__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_1_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__nb_de_chambres</t>
         </is>
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__moyen_de_guests_par_chambre__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__data_a_ajouter_au_futur_calcul_de_simulation</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__moyen_de_guests_par_chambre</t>
         </is>
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__to_annuel_moyen__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__donnees_fictives_pour_le_moment__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_1_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__to_annuel_moyen</t>
         </is>
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__metres_lineaires_dedies_a_votre_corner_actuel_ou_futur__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_4_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__ecran_de_controle_parametres__data__metres_lineaires_dedies_a_votre_corner_actuel_ou_futur</t>
         </is>
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__de_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_2_dans_mes_3_simulateurs_excel_application_d_un_coefficient_moyen_en_fonction_du_type_de_boutique_recommande_a_l_hotel</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__de_produits_f_b</t>
         </is>
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__boissons_non_alcoolisees__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__boissons_non_alcoolisees</t>
         </is>
       </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__boissons_alcoolisees__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__boissons_alcoolisees</t>
         </is>
       </c>
       <c r="EB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sales_secs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sales_secs</t>
         </is>
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sales_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sales_frais</t>
         </is>
       </c>
       <c r="ED1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sucres_secs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sucres_secs</t>
         </is>
       </c>
       <c r="EE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sucres_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sucres_frais</t>
         </is>
       </c>
       <c r="EF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__epicerie_fine__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__epicerie_fine</t>
         </is>
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__de_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_2_dans_mes_3_simulateurs_excel_application_d_un_coefficient_moyen_en_fonction_du_type_de_boutique_recommande_a_l_hotel</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__de_produits_non_f_b</t>
         </is>
       </c>
       <c r="EH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sos__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_sos</t>
         </is>
       </c>
       <c r="EI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__hygiene__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__hygiene</t>
         </is>
       </c>
       <c r="EJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_cosmetiques__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__produits_cosmetiques</t>
         </is>
       </c>
       <c r="EK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__articles_pour_enfants__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__articles_pour_enfants</t>
         </is>
       </c>
       <c r="EL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__pret_a_porter__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__pret_a_porter</t>
         </is>
       </c>
       <c r="EM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__accessoires__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__accessoires</t>
         </is>
       </c>
       <c r="EN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__souvenirs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non_mais_option_ai__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__5_simulateur_de_revenus__sous_etape_rod__mix_produits_choisi_par_l_hotel_dans_un_1er_temps_puis_option_bouton_reco_ia__data__souvenirs</t>
         </is>
       </c>
     </row>
